--- a/data/dividends_info_20261024.xlsx
+++ b/data/dividends_info_20261024.xlsx
@@ -1345,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,7 +1453,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1463,14 +1463,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1514,14 +1514,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1531,24 +1531,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1582,70 +1582,70 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1674,80 +1674,80 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1810,29 +1810,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1844,12 +1844,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1895,12 +1895,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1929,12 +1929,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1946,29 +1946,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1980,12 +1980,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1997,63 +1997,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2065,29 +2065,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2116,12 +2116,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2150,63 +2150,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2296,14 +2296,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2313,19 +2313,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2337,29 +2337,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2405,12 +2405,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2422,12 +2422,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2439,29 +2439,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2473,17 +2473,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2541,7 +2541,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2568,14 +2568,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2609,12 +2609,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2626,12 +2626,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2643,29 +2643,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2677,46 +2677,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2728,12 +2728,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2745,12 +2745,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2762,63 +2762,63 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2847,29 +2847,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2915,46 +2915,46 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2966,46 +2966,46 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3017,12 +3017,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3034,29 +3034,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3068,12 +3068,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3119,29 +3119,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3170,46 +3170,46 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3238,12 +3238,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3255,29 +3255,29 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3289,12 +3289,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3306,12 +3306,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3323,12 +3323,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3340,12 +3340,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3357,29 +3357,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3391,12 +3391,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3408,12 +3408,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3425,29 +3425,29 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3459,29 +3459,29 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3493,12 +3493,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3510,12 +3510,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3527,12 +3527,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3544,41 +3544,41 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3748,7 +3748,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3765,7 +3765,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3792,14 +3792,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3816,7 +3816,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3826,36 +3826,36 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3867,12 +3867,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3884,12 +3884,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3901,12 +3901,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3918,12 +3918,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3935,12 +3935,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3952,63 +3952,63 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4020,46 +4020,46 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4071,63 +4071,63 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4156,12 +4156,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4241,7 +4241,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4285,14 +4285,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4387,14 +4387,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4513,7 +4513,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4632,12 +4632,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4649,29 +4649,29 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4700,12 +4700,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4717,63 +4717,63 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4785,12 +4785,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4802,12 +4802,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4819,29 +4819,29 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4853,46 +4853,46 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4904,12 +4904,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4921,46 +4921,46 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4989,12 +4989,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5006,29 +5006,29 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5040,12 +5040,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5057,12 +5057,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5074,12 +5074,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5091,12 +5091,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5108,29 +5108,29 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5142,12 +5142,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5159,29 +5159,29 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5193,12 +5193,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5210,46 +5210,46 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5261,15 +5261,355 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
+          <t>CY4Gate S.p.A.</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ECOSUNTEK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>EuroGroup Laminations S.p.A.</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>GREEN OLEO S.p.A</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>OMER S.p.A.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CIRCLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Gens Aurea S.p.A.</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Gens Aurea S.p.A.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>H-FARM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CIRCLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PIQUADRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>DHH S.p.A.</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
           <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>2026-11-23</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -5299,44 +5639,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S.S. Lazio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>